--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Monk and Fitzpatrick scales for equitable skin assessment.</t>
+    <t>Skin tone scales for equitable skin assessment. Monk (A-J) is the primary, recommended scale; Fitzpatrick (I-VI) is retained only for backward compatibility with legacy systems.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-onc-skin-tone-vs.xlsx
+++ b/ValueSet-onc-skin-tone-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
